--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raca7784b9de44e84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R616842fb6d7e4226"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R616842fb6d7e4226"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7dc70956e2a48fe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7dc70956e2a48fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R800b39a3b44047b1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R800b39a3b44047b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89f4226506744a2b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89f4226506744a2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd51e350d03e94e02"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd51e350d03e94e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd4dda512768645f7"/>
   </x:sheets>
 </x:workbook>
 </file>
